--- a/output/pdf_financials_xlsx/PAI.xlsx
+++ b/output/pdf_financials_xlsx/PAI.xlsx
@@ -1908,7 +1908,7 @@
         <v>4.244998</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.244998</v>
+        <v>4.308479</v>
       </c>
     </row>
     <row r="93">
@@ -3514,7 +3514,11 @@
           <t>Warrants reserve ( note 13 ) 1,086,433</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4357,7 +4361,11 @@
           <t>Warrants Reserve 9</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PAI.xlsx
+++ b/output/pdf_financials_xlsx/PAI.xlsx
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.28743</v>
+        <v>0.575301</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.65304</v>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.178436</v>
+        <v>-0.466307</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.6412600000000001</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004728</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
         <v>-1.014062</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-9.277108</v>
+        <v>-9.281836</v>
       </c>
     </row>
     <row r="28">
@@ -903,7 +903,7 @@
         <v>-1.013319</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-9.276514000000001</v>
+        <v>-9.281242000000001</v>
       </c>
     </row>
     <row r="30">
@@ -919,7 +919,7 @@
         <v>-8602.028862478779</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-10479.45007399374</v>
+        <v>-10484.79117949413</v>
       </c>
     </row>
     <row r="31">
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.064401</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.009461000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001045</v>
       </c>
     </row>
     <row r="35">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.064401</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.009461000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001045</v>
       </c>
     </row>
     <row r="37">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.069006</v>
+        <v>0.004605</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.021408</v>
+        <v>0.011947</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">

--- a/output/pdf_financials_xlsx/PAI.xlsx
+++ b/output/pdf_financials_xlsx/PAI.xlsx
@@ -7441,7 +7441,11 @@
           <t>Depreciation – property and equipment 6</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
         <v>0.000743</v>
       </c>

--- a/output/pdf_financials_xlsx/PAI.xlsx
+++ b/output/pdf_financials_xlsx/PAI.xlsx
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.053096</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.424949</v>
       </c>
     </row>
     <row r="65">
@@ -3446,7 +3446,11 @@
           <t>Lease liabilities ( note 9 ) 52,491</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -5855,7 +5859,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
